--- a/results/Int Task Remove ACC 0.3/Linea_fi_all.xlsx
+++ b/results/Int Task Remove ACC 0.3/Linea_fi_all.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.010888710968775006 +/- 0.0025931360673661754</t>
+          <t>0.010928742994395502 +/- 0.0025321640673928894</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -906,12 +906,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.0001601281024819823 +/- 0.0008807045636509026</t>
+          <t>8.006405124099114e-05 +/- 0.0008733956857194146</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.00016012810248199337 +/- 0.0012684531239195215</t>
+          <t>-0.00012009607686149781 +/- 0.0012665566068499872</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0.0026020816653322563 +/- 0.0022090279681859725</t>
+          <t>0.0026421136909527522 +/- 0.002164692687685474</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.05836669335468374 +/- 0.004265994172860603</t>
+          <t>0.058326661329063244 +/- 0.004308048627257894</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>0.00048038430744595795 +/- 0.0016775281697163137</t>
+          <t>0.00044035228182546236 +/- 0.0017026557500509625</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-0.006851618327028142 +/- 0.0033524959027474636</t>
+          <t>-0.0068095838587641675 +/- 0.003345901427849101</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1491,12 +1491,12 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>0.1867591424968474 +/- 0.008722633268914367</t>
+          <t>0.1867171080285835 +/- 0.00875851468054745</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.16729718369062635 +/- 0.006937597658100978</t>
+          <t>0.16733921815889033 +/- 0.006994540571343621</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.040419287211740026 +/- 0.00443811106831002</t>
+          <t>0.04046121593291404 +/- 0.004477744008334188</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1801,72 +1801,72 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>-0.00046121593291404973 +/- 0.0007832931527156801</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0.06327044025157234 +/- 0.005829298700218227</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0.0009224318658280883 +/- 0.0025968742251072366</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0.0009224318658280883 +/- 0.0025968742251072366</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>-0.020712788259958058 +/- 0.0036417695179217424</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0.10025157232704407 +/- 0.004498113520214731</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0.006331236897274639 +/- 0.0018886550322105224</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0.02360587002096436 +/- 0.005662861478357148</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>-0.02997903563941299 +/- 0.004156022557987206</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>0.021425576519916147 +/- 0.003961986834881841</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0.5080922431865827 +/- 0.00732685657318332</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>-0.009685534591194955 +/- 0.003733540145825356</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>0.09350104821802938 +/- 0.0069277616946995055</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
           <t>-0.00046121593291404973 +/- 0.0008054244323814689</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>0.06327044025157234 +/- 0.005829298700218227</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0.0009224318658280883 +/- 0.0025968742251072366</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>0.0009224318658280883 +/- 0.0025968742251072366</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>-0.020712788259958058 +/- 0.0036417695179217424</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0.10025157232704407 +/- 0.004498113520214731</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0.006331236897274639 +/- 0.0018886550322105224</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0.02360587002096436 +/- 0.005662861478357148</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>-0.02997903563941299 +/- 0.004156022557987206</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>0.021425576519916147 +/- 0.003961986834881841</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>0.5080922431865827 +/- 0.00732685657318332</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>-0.009685534591194955 +/- 0.003733540145825356</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>0.09350104821802938 +/- 0.0069277616946995055</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>-0.0005031446540880502 +/- 0.0007685661542902692</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>0.01816334823242587 +/- 0.002570233986325647</t>
+          <t>0.018122714343762725 +/- 0.0025711974026097436</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>0.04756554307116105 +/- 0.007205585675998884</t>
+          <t>0.047607157719517276 +/- 0.0072466864922314566</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.043726395300042006 +/- 0.004875043468386952</t>
+          <t>0.043684431389005504 +/- 0.004852051694934666</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.045446915652538854 +/- 0.004531519522364029</t>
+          <t>0.04540495174150235 +/- 0.004495429875230239</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>0.030423835501468776 +/- 0.0044062106588334095</t>
+          <t>0.030465799412505278 +/- 0.004461614388586489</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>-0.048929920268568995 +/- 0.0018879096733868089</t>
+          <t>-0.04888795635753249 +/- 0.0018696323466173175</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3561,7 +3561,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.06290050590219229 +/- 0.007557553403135441</t>
+          <t>0.06285834738617205 +/- 0.007500069908399461</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.06913996627318725 +/- 0.007379546875899188</t>
+          <t>0.06913996627318723 +/- 0.007326368970060207</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-0.003972950126796293 +/- 0.00554048000276379</t>
+          <t>-0.004015215553677098 +/- 0.0055438643880891605</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
